--- a/data/output/naic.xlsx
+++ b/data/output/naic.xlsx
@@ -7,6 +7,10 @@
     <sheet name="Coverage" sheetId="3" r:id="rId3"/>
     <sheet name="Safe Cores" sheetId="4" r:id="rId4"/>
     <sheet name="Threats" sheetId="5" r:id="rId5"/>
+    <sheet name="Lineups" sheetId="6" r:id="rId6"/>
+    <sheet name="Lineup Resources" sheetId="7" r:id="rId7"/>
+    <sheet name="Bench Utility" sheetId="8" r:id="rId8"/>
+    <sheet name="Bench Warnings" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -177,67 +181,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dominate_count</t>
+          <t>defensive_type_score</t>
         </is>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>-20.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dominate_rate</t>
+          <t>dominate_count</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.8888888888888888</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>full_col_coverage</t>
+          <t>dominate_rate</t>
         </is>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mean_best_score</t>
+          <t>full_col_coverage</t>
         </is>
       </c>
       <c r="B10">
-        <v>745.5555555555555</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>no_cover_pairs</t>
+          <t>legacy_full_roster_dominate_count</t>
         </is>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>no_cover_rate</t>
+          <t>legacy_full_roster_mean_best_score</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.0</v>
+        <v>745.5555555555555</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>overwhelming_count</t>
+          <t>legacy_full_roster_overwhelming_count</t>
         </is>
       </c>
       <c r="B13">
@@ -247,162 +251,262 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>overwhelming_rate</t>
+          <t>lineup_best_score</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.0</v>
+        <v>709.9444444444445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pair_coverage</t>
+          <t>lineup_objective_score</t>
         </is>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>617.8461111111111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>redundant_coverage_2plus</t>
+          <t>lineup_top_n_mean_score</t>
         </is>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>708.4277777777777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>redundant_coverage_3plus</t>
+          <t>lineup_viable_count</t>
         </is>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>safe_member_floor</t>
+          <t>mean_best_score</t>
         </is>
       </c>
       <c r="B18">
-        <v>90.0</v>
+        <v>745.5555555555555</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>safe_member_target</t>
+          <t>no_cover_pairs</t>
         </is>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>safety_floor_target</t>
+          <t>no_cover_rate</t>
         </is>
       </c>
       <c r="B20">
-        <v>78.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>safety_pool_max</t>
+          <t>offensive_move_score</t>
         </is>
       </c>
       <c r="B21">
-        <v>97.6</v>
+        <v>27.20000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>safety_pool_mean</t>
+          <t>overwhelming_count</t>
         </is>
       </c>
       <c r="B22">
-        <v>88.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>safety_pool_min</t>
+          <t>overwhelming_rate</t>
         </is>
       </c>
       <c r="B23">
-        <v>79.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>safety_priority</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>pair_coverage</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>safety_score</t>
+          <t>ranking_aware_score</t>
         </is>
       </c>
       <c r="B25">
-        <v>88.5</v>
+        <v>0.7530468161283232</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>single_cover_pairs</t>
+          <t>redundant_coverage_2plus</t>
         </is>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>single_cover_rate</t>
+          <t>redundant_coverage_3plus</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.16666666666666666</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>total_pairs</t>
+          <t>safe_member_floor</t>
         </is>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>safe_member_target</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>safety_floor_target</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>78.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>safety_pool_max</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>97.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>safety_pool_mean</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>safety_pool_min</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>safety_priority</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>safety_score</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>single_cover_pairs</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>single_cover_rate</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_pairs</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>weighted_worst_best_score</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B39">
         <v>669.6666666666667</v>
       </c>
     </row>
@@ -525,256 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Castform H+WBR/EB 4/15/14</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+DyP/SB 4/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Castform H+WBR/EB 4/15/14</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+DyP/SB 4/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ABA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Castform H+WBR/EB 4/15/14</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Dubwool DK+BS/Pbk 5/14/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Dubwool DK+BS/Pbk 5/14/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Castform H+WBR/EB 4/15/14</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+DyP/SB 4/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ABA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Castform H+WBR/EB 4/15/14</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Raichu (Alolan) TS+WC/TBl 6/14/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Raichu (Alolan) TS+WC/TBl 6/14/15</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+DyP/SB 4/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dubwool DK+BS/Pbk 5/14/14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+DyP/SB 4/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Raichu (Alolan) TS+WC/TBl 6/14/15</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hypno Cf+SB/TP 5/13/14</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -860,4 +714,1305 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Back 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Back 2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Team Shape</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lineup Score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mean Score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dominating Matchups</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Overwhelming Matchups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Raichu (Alolan) TS+WC/TBl 6/14/15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>716.2133842054234</v>
+      </c>
+      <c r="G2">
+        <v>709.9444444444443</v>
+      </c>
+      <c r="H2">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+DyP/SB 4/15/15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>714.7567084315642</v>
+      </c>
+      <c r="G3">
+        <v>708.2777777777778</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Raichu (Alolan) TS+WC/TBl 6/14/15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>714.4328710732575</v>
+      </c>
+      <c r="G4">
+        <v>709.9444444444445</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Castform H+WBR/EB 4/15/14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>714.4264003241032</v>
+      </c>
+      <c r="G5">
+        <v>709.1666666666666</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Castform H+WBR/EB 4/15/14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>713.8832204758897</v>
+      </c>
+      <c r="G6">
+        <v>709.0555555555555</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+DyP/SB 4/15/15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>713.7741641079357</v>
+      </c>
+      <c r="G7">
+        <v>708.2777777777777</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+DyP/SB 4/15/15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>713.6674431090084</v>
+      </c>
+      <c r="G8">
+        <v>708.2777777777777</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dubwool DK+BS/Pbk 5/14/14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>713.4287181507322</v>
+      </c>
+      <c r="G9">
+        <v>708.0555555555555</v>
+      </c>
+      <c r="H9">
+        <v>16</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Castform H+WBR/EB 4/15/14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>713.2293572237697</v>
+      </c>
+      <c r="G10">
+        <v>709.0555555555555</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hypno Cf+SB/TP 5/13/14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Raichu (Alolan) TS+WC/TBl 6/14/15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Weezing (Galarian) FW+Sl/BrS 4/14/13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>709.809914173591</v>
+      </c>
+      <c r="G11">
+        <v>704.0555555555555</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lineup Rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lead Shield</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Back Shield</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Best Score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dominating Matchups</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Overwhelming Matchups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>665.0</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>686.6666666666666</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>778.1666666666666</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>655.6666666666666</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>705.3333333333334</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>763.8333333333334</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>665.0</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>758.3333333333334</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>706.5</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>692.1666666666666</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>707.1666666666666</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>728.1666666666666</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>692.1666666666666</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>686.6666666666666</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>748.3333333333334</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>655.6666666666666</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>722.6666666666666</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>746.5</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>655.6666666666666</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>726.6666666666666</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>742.5</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>655.6666666666666</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>725.6666666666666</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>742.8333333333334</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>692.1666666666666</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>9</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>728.5</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>706.5</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>10</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>665.0</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>10</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>725.5</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>10</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>721.6666666666666</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lineups Used</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Lead Lineups Used</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Back Lineups Used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Viable Lineup Rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>All Lineup Rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best Lineup Score</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>